--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487796_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487796_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3782</v>
+        <v>5.0798</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4057</v>
+        <v>4.0487</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9724</v>
+        <v>1.0311</v>
       </c>
       <c r="G2" t="n">
         <v>4.0252</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4795</v>
+        <v>0.2222</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7829</v>
+        <v>-0.14</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3034</v>
+        <v>0.3621</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6593</v>
+        <v>3.3594</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7492</v>
+        <v>1.3561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9101</v>
+        <v>2.0033</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7941</v>
+        <v>2.6971</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2665</v>
+        <v>0.8487</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5275</v>
+        <v>1.8484</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2677</v>
+        <v>1.8766</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9934</v>
+        <v>0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2743</v>
+        <v>1.1667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5264</v>
+        <v>0.8205</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7268</v>
+        <v>0.1387</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2532</v>
+        <v>0.6817</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0109</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2703</v>
+        <v>0.5201</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7405</v>
+        <v>0.3504</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1051</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2992</v>
+        <v>3.1225</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6776</v>
+        <v>1.4827</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6216</v>
+        <v>1.6398</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6971</v>
+        <v>1.2868</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8487</v>
+        <v>0.3602</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8484</v>
+        <v>0.9266</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8766</v>
+        <v>0.944</v>
       </c>
       <c r="K4" t="n">
-        <v>0.71</v>
+        <v>0.4133</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1667</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8205</v>
+        <v>0.3428</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1387</v>
+        <v>-0.0532</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6817</v>
+        <v>0.396</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8103</v>
+        <v>1.4195</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8416</v>
+        <v>0.5387</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0313</v>
+        <v>0.8808</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2884</v>
+        <v>2.6564</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5898</v>
+        <v>2.4331</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6986</v>
+        <v>0.2234</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2868</v>
+        <v>0.9352</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3602</v>
+        <v>-0.8764</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9266</v>
+        <v>1.8116</v>
       </c>
       <c r="J5" t="n">
-        <v>0.944</v>
+        <v>2.0375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4133</v>
+        <v>0.0871</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5306999999999999</v>
+        <v>1.9504</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3428</v>
+        <v>-1.1023</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0532</v>
+        <v>-0.9636</v>
       </c>
       <c r="O5" t="n">
-        <v>0.396</v>
+        <v>-0.1388</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5853</v>
+        <v>0.3237</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6458</v>
+        <v>0.0386</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9395</v>
+        <v>0.2851</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4025</v>
+        <v>2.002</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3259</v>
+        <v>1.3562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0766</v>
+        <v>0.6458</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9352</v>
+        <v>3.7941</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8764</v>
+        <v>2.2665</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8116</v>
+        <v>1.5275</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0375</v>
+        <v>3.2677</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0871</v>
+        <v>2.9934</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9504</v>
+        <v>0.2743</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1023</v>
+        <v>0.5264</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9636</v>
+        <v>-0.7268</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1388</v>
+        <v>1.2532</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0698</v>
+        <v>1.3536</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.8773</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1383</v>
+        <v>0.4763</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3975</v>
+        <v>-2.1051</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3975</v>
+        <v>-0.7076</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.105</v>
+        <v>0.7336</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6056</v>
+        <v>-1.7128</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7107</v>
+        <v>2.4464</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1943</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>1.113</v>
+        <v>0.7416</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1272</v>
+        <v>0.02</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9858</v>
+        <v>0.7216</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SIENCHE GUEMETA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9469</v>
+        <v>0.1581</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0791</v>
+        <v>-1.9259</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1322</v>
+        <v>2.084</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8517</v>
+        <v>1.271</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1727</v>
+        <v>-1.3473</v>
       </c>
       <c r="I8" t="n">
-        <v>1.321</v>
+        <v>2.6183</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3209</v>
+        <v>0.6262</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.352</v>
+        <v>-0.5225</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0311</v>
+        <v>1.1487</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5308</v>
+        <v>0.6448</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8207</v>
+        <v>-0.8248</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2898</v>
+        <v>1.4696</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3033</v>
+        <v>1.1764</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>0.5696</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4143</v>
+        <v>0.6068</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>J. SIENCHE GUEMETA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0118</v>
+        <v>-0.5682</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8903</v>
+        <v>-1.4362</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8785</v>
+        <v>0.868</v>
       </c>
       <c r="G9" t="n">
-        <v>1.271</v>
+        <v>-0.8517</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3473</v>
+        <v>-2.1727</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6183</v>
+        <v>1.321</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6262</v>
+        <v>-0.3209</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5225</v>
+        <v>-1.352</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1487</v>
+        <v>1.0311</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6448</v>
+        <v>-0.5308</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8248</v>
+        <v>-0.8207</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4696</v>
+        <v>0.2898</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0065</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3948</v>
+        <v>-0.0747</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4013</v>
+        <v>0.1501</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>L. SORENSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.117</v>
+        <v>-0.6876</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4086</v>
+        <v>-2.262</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2916</v>
+        <v>1.5744</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0873</v>
+        <v>-1.36</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8979</v>
+        <v>-0.6571</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1894</v>
+        <v>-0.7029</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7035</v>
+        <v>-2.7724</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9387</v>
+        <v>-0.7468</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2351</v>
+        <v>-2.0256</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3838</v>
+        <v>1.4123</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0407</v>
+        <v>0.0897</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4245</v>
+        <v>1.3226</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1379</v>
+        <v>1.0887</v>
       </c>
       <c r="T10" t="n">
-        <v>1.295</v>
+        <v>0.3834</v>
       </c>
       <c r="U10" t="n">
-        <v>0.843</v>
+        <v>0.7053</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. SORENSEN</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1265</v>
+        <v>-2.4528</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5835</v>
+        <v>-2.4801</v>
       </c>
       <c r="F11" t="n">
-        <v>1.457</v>
+        <v>0.0274</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.36</v>
+        <v>-3.0873</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6571</v>
+        <v>-2.8979</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7029</v>
+        <v>-0.1894</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7724</v>
+        <v>-2.7035</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7468</v>
+        <v>-2.9387</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0256</v>
+        <v>0.2351</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4123</v>
+        <v>-0.3838</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0897</v>
+        <v>0.0407</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3226</v>
+        <v>-0.4245</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6498</v>
+        <v>0.8021</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0619</v>
+        <v>0.2234</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5878</v>
+        <v>0.5787</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4553</v>
+        <v>-5.9283</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8409</v>
+        <v>-5.5194</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6145</v>
+        <v>-0.4089</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2502</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5402</v>
+        <v>-0.0132</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1487</v>
+        <v>0.0568</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.475099999999999</v>
+        <v>7.474899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.659800000000001</v>
+        <v>-4.659600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1348</v>
+        <v>12.1347</v>
       </c>
       <c r="G13" t="n">
         <v>6.265900000000002</v>
@@ -1441,7 +1441,7 @@
         <v>14.614</v>
       </c>
       <c r="J13" t="n">
-        <v>4.124100000000002</v>
+        <v>4.124099999999997</v>
       </c>
       <c r="K13" t="n">
         <v>-4.2033</v>
@@ -1468,13 +1468,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>8.060499999999999</v>
+        <v>8.060500000000001</v>
       </c>
       <c r="T13" t="n">
         <v>2.8864</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1739</v>
+        <v>5.174</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6879</v>
+        <v>2.2108</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1432</v>
+        <v>-0.3926</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5447</v>
+        <v>2.6034</v>
       </c>
       <c r="G14" t="n">
         <v>1.0186</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2871</v>
+        <v>-0.7641</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2023</v>
+        <v>-0.7381</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0847</v>
+        <v>-0.026</v>
       </c>
       <c r="V14" t="n">
         <v>0.7076</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GARZON JIMENEZ</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8669</v>
+        <v>0.8266</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6231</v>
+        <v>-0.551</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2438</v>
+        <v>1.3776</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1779</v>
+        <v>3.3342</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4328</v>
+        <v>2.5137</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6107</v>
+        <v>0.8205</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0392</v>
+        <v>4.4038</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.5218</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0392</v>
+        <v>2.882</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1387</v>
+        <v>-1.0696</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4328</v>
+        <v>0.9918</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5715</v>
+        <v>-2.0614</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6889</v>
+        <v>-0.6345</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5839</v>
+        <v>-0.7924</v>
       </c>
       <c r="U16" t="n">
-        <v>0.105</v>
+        <v>0.1579</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>J. GARZON JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2718</v>
+        <v>0.3208</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1939</v>
+        <v>0.1945</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4657</v>
+        <v>0.1263</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3342</v>
+        <v>0.1779</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5137</v>
+        <v>-0.4328</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8205</v>
+        <v>0.6107</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4038</v>
+        <v>0.0392</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5218</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.882</v>
+        <v>0.0392</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0696</v>
+        <v>0.1387</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9918</v>
+        <v>-0.4328</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0614</v>
+        <v>0.5715</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8731</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1893</v>
+        <v>0.1429</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4354</v>
+        <v>0.1553</v>
       </c>
       <c r="U17" t="n">
-        <v>0.246</v>
+        <v>-0.0124</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.6773</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7847</v>
+        <v>0.0176</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6856</v>
+        <v>-0.6949</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.459</v>
+        <v>0.8074</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0171</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4761</v>
+        <v>0.191</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9118000000000001</v>
+        <v>1.5382</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0686</v>
+        <v>0.9594</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1568</v>
+        <v>0.5788</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5471</v>
+        <v>-0.7308</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0857</v>
+        <v>-0.3431</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6328</v>
+        <v>-0.3878</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4974</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6106</v>
+        <v>-1.0685</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7078</v>
+        <v>-0.48</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.5884</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7257</v>
+        <v>-0.8458</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0895</v>
+        <v>-1.9386</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6362</v>
+        <v>1.0927</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8074</v>
+        <v>-1.5221</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.4072</v>
       </c>
       <c r="I19" t="n">
-        <v>0.191</v>
+        <v>-2.9293</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5382</v>
+        <v>-2.1262</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9594</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5788</v>
+        <v>-2.8273</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7308</v>
+        <v>0.604</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3431</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3878</v>
+        <v>-0.102</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1169</v>
+        <v>-0.74</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3962</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.3438</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2554</v>
+        <v>-1.4055</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2601</v>
+        <v>-1.8563</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0047</v>
+        <v>0.4508</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5221</v>
+        <v>-1.459</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4072</v>
+        <v>0.0171</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9293</v>
+        <v>-1.4761</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1262</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7010999999999999</v>
+        <v>-1.0686</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.8273</v>
+        <v>0.1568</v>
       </c>
       <c r="M20" t="n">
-        <v>0.604</v>
+        <v>-0.5471</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.0857</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.102</v>
+        <v>-1.6328</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1495</v>
+        <v>-0.6958</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>-0.3638</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4318</v>
+        <v>-0.332</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5838</v>
+        <v>-0.7076</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>0.4599</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7848</v>
+        <v>-1.6101</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8561</v>
+        <v>-1.5346</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0713</v>
+        <v>-0.0755</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0907</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7347</v>
+        <v>-1.5601</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3701</v>
+        <v>-1.0486</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3646</v>
+        <v>-0.5114</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2712</v>
+        <v>-1.9292</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2965</v>
+        <v>-2.1893</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0253</v>
+        <v>0.2602</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8933</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7941</v>
+        <v>-1.4521</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8482</v>
+        <v>-0.741</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9459</v>
+        <v>-0.7111</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2838</v>
+        <v>-5.4838</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5877</v>
+        <v>-5.0519</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4318</v>
       </c>
       <c r="G23" t="n">
         <v>-6.7327</v>
@@ -2248,13 +2248,13 @@
         <v>2.4974</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9455</v>
+        <v>-1.1455</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3049</v>
+        <v>-0.7691</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.3764</v>
       </c>
       <c r="V23" t="n">
         <v>0.9376</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4749</v>
+        <v>-7.475</v>
       </c>
       <c r="E24" t="n">
         <v>-12.1347</v>
       </c>
       <c r="F24" t="n">
-        <v>4.6598</v>
+        <v>4.659800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-6.2658</v>
@@ -2311,7 +2311,7 @@
         <v>-4.124000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2032</v>
+        <v>4.203199999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-8.327400000000001</v>
@@ -2326,13 +2326,13 @@
         <v>13.5277</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.060500000000001</v>
+        <v>-8.060599999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.174099999999999</v>
+        <v>-5.1739</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.8863</v>
+        <v>-2.8865</v>
       </c>
       <c r="V24" t="n">
         <v>2.6889</v>
